--- a/public/templates/examples/A-005-RACIMatrixForCybersecurity-EXAMPLE-M.xlsx
+++ b/public/templates/examples/A-005-RACIMatrixForCybersecurity-EXAMPLE-M.xlsx
@@ -4,11 +4,10 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -661,7 +660,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Authority</t>
@@ -736,7 +735,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="50.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>This matrix maps each cybersecurity function at Wabash Valley Communications to the roles that carry it. The Director is accountable for governance and oversight; the part-time security coordinator is accountable for day-to-day security operations; the shared county IT team does much of the technical work; and the annual audit is contracted for independence.</t>
@@ -750,14 +749,14 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Each row is a security function; each column is a role. R = Responsible (does the work); A = Accountable (owns the outcome, one per row); C = Consulted (gives input); I = Informed (kept up to date).</t>
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>At Wabash Valley Communications the Director and the security coordinator split the accountable role between governance and operations. The contracted reviewer provides the independence the audit row needs. Columns map to the Security Role Descriptions.</t>
@@ -771,7 +770,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="50.5" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Security Function \ Role</t>
@@ -808,7 +807,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="34.7" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Set security &amp; privacy priorities</t>
@@ -993,7 +992,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="34.7" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Secure configuration &amp; patching</t>
@@ -1333,7 +1332,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="50.5" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
           <t>The annual access and control review (row 14) is performed by a contracted independent reviewer, recorded in the IT Support Accountability Agreement. The CAD and ESInet vendors carry the Responsible role for configuration and backup on the systems they operate. The security coordinator’s part-time status caps monitoring depth; a managed detection service is under evaluation.</t>
@@ -1382,7 +1381,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="34.7" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>Version</t>
@@ -1404,7 +1403,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="34.7" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -1453,67 +1452,8 @@
     <mergeCell ref="A33:G33"/>
     <mergeCell ref="C3:G3"/>
   </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="95" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>RACI Matrix: How to use</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Rows: each is a major cybersecurity function the center performs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Columns: each is a role. They map to the Security Role Descriptions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Cells use RACI: R Responsible, A Accountable (one per row), C Consulted, I Informed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>The Director is Accountable for governance; the security coordinator is Accountable for security operations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>The annual audit is contracted to an independent reviewer for independence.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>